--- a/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
+++ b/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T14:00:09+00:00</t>
+    <t>2025-04-15T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
+++ b/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T15:06:38+00:00</t>
+    <t>2025-04-17T14:33:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
+++ b/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T14:33:47+00:00</t>
+    <t>2025-04-18T09:50:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
+++ b/ig/DM-AVRIL-2025/ASS-X01-TranscoSavFaireADELI-SavFaireR01.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:50:48+00:00</t>
+    <t>2025-04-22T11:23:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
